--- a/data/broker/broker_quote_2026-08-07.xlsx
+++ b/data/broker/broker_quote_2026-08-07.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="564">
   <si>
     <t>类型</t>
   </si>
@@ -165,6 +165,153 @@
     <t>2025-04-23</t>
   </si>
   <si>
+    <t>24泰丰02</t>
+  </si>
+  <si>
+    <t>254402.SH</t>
+  </si>
+  <si>
+    <t>2.75Y</t>
+  </si>
+  <si>
+    <t>3.0200</t>
+  </si>
+  <si>
+    <t>2.9625</t>
+  </si>
+  <si>
+    <t>03:02:43</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>新泰市财金投资集团有限公司</t>
+  </si>
+  <si>
+    <t>107.4851</t>
+  </si>
+  <si>
+    <t>19.36</t>
+  </si>
+  <si>
+    <t>11621.43</t>
+  </si>
+  <si>
+    <t>7/14</t>
+  </si>
+  <si>
+    <t>申港证券股份有限公司</t>
+  </si>
+  <si>
+    <t>2024-05-07</t>
+  </si>
+  <si>
+    <t>25青岛上合PPN003</t>
+  </si>
+  <si>
+    <t>032501380.IB</t>
+  </si>
+  <si>
+    <t>2.30Y</t>
+  </si>
+  <si>
+    <t>2.9500</t>
+  </si>
+  <si>
+    <t>3.0444</t>
+  </si>
+  <si>
+    <t>-9.44</t>
+  </si>
+  <si>
+    <t>07:04:14</t>
+  </si>
+  <si>
+    <t>D+</t>
+  </si>
+  <si>
+    <t>98.4495</t>
+  </si>
+  <si>
+    <t>中国国际金融股份有限公司</t>
+  </si>
+  <si>
+    <t>2025-11-20</t>
+  </si>
+  <si>
+    <t>26津资08</t>
+  </si>
+  <si>
+    <t>282813.SH</t>
+  </si>
+  <si>
+    <t>4.82Y</t>
+  </si>
+  <si>
+    <t>2.8500</t>
+  </si>
+  <si>
+    <t>2.9200</t>
+  </si>
+  <si>
+    <t>-7.00</t>
+  </si>
+  <si>
+    <t>2.8661</t>
+  </si>
+  <si>
+    <t>-1.61</t>
+  </si>
+  <si>
+    <t>08:40:33</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>98.1241</t>
+  </si>
+  <si>
+    <t>36.73</t>
+  </si>
+  <si>
+    <t>36722.39</t>
+  </si>
+  <si>
+    <t>浙商证券股份有限公司</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>24首开MTN001</t>
+  </si>
+  <si>
+    <t>102480110.IB</t>
+  </si>
+  <si>
+    <t>158D+2.00Y</t>
+  </si>
+  <si>
+    <t>2.8555/3.2434</t>
+  </si>
+  <si>
+    <t>-0.55</t>
+  </si>
+  <si>
+    <t>07:32:40</t>
+  </si>
+  <si>
+    <t>100.3090</t>
+  </si>
+  <si>
+    <t>中国银行股份有限公司</t>
+  </si>
+  <si>
+    <t>2024-01-09</t>
+  </si>
+  <si>
     <t>成交日期</t>
   </si>
   <si>
@@ -186,6 +333,30 @@
     <t>浙江</t>
   </si>
   <si>
+    <t>5.75</t>
+  </si>
+  <si>
+    <t>山东泰丰控股集团有限公司</t>
+  </si>
+  <si>
+    <t>山东</t>
+  </si>
+  <si>
+    <t>青岛上合控股发展集团有限公司</t>
+  </si>
+  <si>
+    <t>天津渤海国有资产经营管理有限公司</t>
+  </si>
+  <si>
+    <t>天津</t>
+  </si>
+  <si>
+    <t>北京首都开发股份有限公司</t>
+  </si>
+  <si>
+    <t>北京</t>
+  </si>
+  <si>
     <t>2026-7-22</t>
   </si>
   <si>
@@ -291,9 +462,6 @@
     <t>9.85Y</t>
   </si>
   <si>
-    <t>3.0200</t>
-  </si>
-  <si>
     <t>2.9578</t>
   </si>
   <si>
@@ -309,9 +477,6 @@
     <t>102681950.IB</t>
   </si>
   <si>
-    <t>24泰丰02</t>
-  </si>
-  <si>
     <t>2.79Y</t>
   </si>
   <si>
@@ -321,15 +486,6 @@
     <t>4.04</t>
   </si>
   <si>
-    <t>山东泰丰控股集团有限公司</t>
-  </si>
-  <si>
-    <t>山东</t>
-  </si>
-  <si>
-    <t>254402.SH</t>
-  </si>
-  <si>
     <t>25陕建集团SCP012(科创债)</t>
   </si>
   <si>
@@ -357,12 +513,6 @@
     <t>26鲁商MTN001</t>
   </si>
   <si>
-    <t>2.75Y</t>
-  </si>
-  <si>
-    <t>2.8500</t>
-  </si>
-  <si>
     <t>2.7675</t>
   </si>
   <si>
@@ -393,12 +543,6 @@
     <t>1.89</t>
   </si>
   <si>
-    <t>北京首都开发股份有限公司</t>
-  </si>
-  <si>
-    <t>北京</t>
-  </si>
-  <si>
     <t>259691.SH</t>
   </si>
   <si>
@@ -426,9 +570,6 @@
     <t>-2.39</t>
   </si>
   <si>
-    <t>青岛上合控股发展集团有限公司</t>
-  </si>
-  <si>
     <t>254483.SH</t>
   </si>
   <si>
@@ -618,21 +759,12 @@
     <t>4.74Y</t>
   </si>
   <si>
-    <t>2.9500</t>
-  </si>
-  <si>
     <t>2.9767</t>
   </si>
   <si>
     <t>-2.67</t>
   </si>
   <si>
-    <t>天津渤海国有资产经营管理有限公司</t>
-  </si>
-  <si>
-    <t>天津</t>
-  </si>
-  <si>
     <t>282465.SH</t>
   </si>
   <si>
@@ -1326,22 +1458,13 @@
     <t>102602044.IB</t>
   </si>
   <si>
-    <t>26津资08</t>
-  </si>
-  <si>
     <t>4.83Y</t>
   </si>
   <si>
-    <t>2.9200</t>
-  </si>
-  <si>
     <t>2.9693</t>
   </si>
   <si>
     <t>-4.93</t>
-  </si>
-  <si>
-    <t>282813.SH</t>
   </si>
   <si>
     <t>24蓝创01</t>
@@ -1958,18 +2081,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="14" width="10" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
     <col min="17" max="17" width="10" customWidth="1"/>
     <col min="18" max="18" width="12" customWidth="1"/>
-    <col min="19" max="19" width="10" customWidth="1"/>
+    <col min="19" max="19" width="28" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
     <col min="21" max="21" width="10" customWidth="1"/>
     <col min="22" max="22" width="14" customWidth="1"/>
@@ -1977,7 +2101,7 @@
     <col min="24" max="24" width="18" customWidth="1"/>
     <col min="25" max="25" width="19" customWidth="1"/>
     <col min="26" max="26" width="13" customWidth="1"/>
-    <col min="27" max="27" width="22" customWidth="1"/>
+    <col min="27" max="27" width="26" customWidth="1"/>
     <col min="28" max="28" width="14" customWidth="1"/>
     <col min="29" max="29" width="12" customWidth="1"/>
     <col min="30" max="30" width="10" customWidth="1"/>
@@ -2167,6 +2291,374 @@
         <v>30</v>
       </c>
     </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S3" t="s">
+        <v>57</v>
+      </c>
+      <c r="T3" t="s">
+        <v>42</v>
+      </c>
+      <c r="U3" t="s">
+        <v>58</v>
+      </c>
+      <c r="V3" t="s">
+        <v>59</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" t="s">
+        <v>68</v>
+      </c>
+      <c r="P4" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>70</v>
+      </c>
+      <c r="R4" t="s">
+        <v>71</v>
+      </c>
+      <c r="S4" t="s">
+        <v>41</v>
+      </c>
+      <c r="T4" t="s">
+        <v>42</v>
+      </c>
+      <c r="U4" t="s">
+        <v>72</v>
+      </c>
+      <c r="V4" t="s">
+        <v>41</v>
+      </c>
+      <c r="W4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K5" t="s">
+        <v>80</v>
+      </c>
+      <c r="L5" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" t="s">
+        <v>36</v>
+      </c>
+      <c r="O5" t="s">
+        <v>81</v>
+      </c>
+      <c r="P5" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>83</v>
+      </c>
+      <c r="R5" t="s">
+        <v>84</v>
+      </c>
+      <c r="S5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T5" t="s">
+        <v>42</v>
+      </c>
+      <c r="U5" t="s">
+        <v>85</v>
+      </c>
+      <c r="V5" t="s">
+        <v>86</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" t="s">
+        <v>78</v>
+      </c>
+      <c r="J6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" t="s">
+        <v>36</v>
+      </c>
+      <c r="O6" t="s">
+        <v>93</v>
+      </c>
+      <c r="P6" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>95</v>
+      </c>
+      <c r="R6" t="s">
+        <v>71</v>
+      </c>
+      <c r="S6" t="s">
+        <v>41</v>
+      </c>
+      <c r="T6" t="s">
+        <v>42</v>
+      </c>
+      <c r="U6" t="s">
+        <v>96</v>
+      </c>
+      <c r="V6" t="s">
+        <v>41</v>
+      </c>
+      <c r="W6" t="s">
+        <v>41</v>
+      </c>
+      <c r="X6" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2175,15 +2667,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
@@ -2191,7 +2684,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2209,10 +2702,10 @@
         <v>15</v>
       </c>
       <c r="G1" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="H1" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="I1" t="s">
         <v>2</v>
@@ -2226,7 +2719,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -2241,13 +2734,13 @@
         <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="H2" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="I2" t="s">
         <v>32</v>
@@ -2256,6 +2749,146 @@
         <v>42</v>
       </c>
       <c r="K2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I4" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K6" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2267,7 +2900,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2284,7 +2917,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2302,10 +2935,10 @@
         <v>15</v>
       </c>
       <c r="G1" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="H1" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="I1" t="s">
         <v>2</v>
@@ -2319,31 +2952,31 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="I2" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="J2" t="s">
         <v>42</v>
@@ -2354,31 +2987,31 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="I3" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="J3" t="s">
         <v>42</v>
@@ -2389,31 +3022,31 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="G4" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="H4" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="I4" t="s">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="J4" t="s">
         <v>42</v>
@@ -2424,31 +3057,31 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="F5" t="s">
-        <v>86</v>
+        <v>143</v>
       </c>
       <c r="G5" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="H5" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="I5" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="J5" t="s">
         <v>42</v>
@@ -2459,31 +3092,31 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>93</v>
+        <v>149</v>
       </c>
       <c r="F6" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="G6" t="s">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="H6" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="I6" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="J6" t="s">
         <v>42</v>
@@ -2494,31 +3127,31 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="F7" t="s">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="G7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H7" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I7" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="J7" t="s">
         <v>42</v>
@@ -2529,31 +3162,31 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="E8" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="F8" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
       <c r="G8" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="H8" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="I8" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="J8" t="s">
         <v>42</v>
@@ -2564,31 +3197,31 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="F9" t="s">
-        <v>117</v>
+        <v>167</v>
       </c>
       <c r="G9" t="s">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="H9" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I9" t="s">
-        <v>119</v>
+        <v>169</v>
       </c>
       <c r="J9" t="s">
         <v>42</v>
@@ -2599,31 +3232,31 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>171</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>172</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>173</v>
       </c>
       <c r="E10" t="s">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="F10" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="G10" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="H10" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I10" t="s">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="J10" t="s">
         <v>42</v>
@@ -2634,31 +3267,31 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" t="s">
+        <v>179</v>
+      </c>
+      <c r="F11" t="s">
+        <v>180</v>
+      </c>
+      <c r="G11" t="s">
         <v>120</v>
       </c>
-      <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D11" t="s">
-        <v>130</v>
-      </c>
-      <c r="E11" t="s">
-        <v>131</v>
-      </c>
-      <c r="F11" t="s">
-        <v>132</v>
-      </c>
-      <c r="G11" t="s">
-        <v>63</v>
-      </c>
       <c r="H11" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="I11" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="J11" t="s">
         <v>42</v>
@@ -2669,31 +3302,31 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="B12" t="s">
-        <v>133</v>
+        <v>181</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>182</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="E12" t="s">
-        <v>135</v>
+        <v>183</v>
       </c>
       <c r="F12" t="s">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="G12" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="H12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I12" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="J12" t="s">
         <v>42</v>
@@ -2704,31 +3337,31 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="C13" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="E13" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="G13" t="s">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="H13" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="I13" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="J13" t="s">
         <v>42</v>
@@ -2739,31 +3372,31 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="C14" t="s">
-        <v>147</v>
+        <v>194</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="E14" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="F14" t="s">
-        <v>150</v>
+        <v>197</v>
       </c>
       <c r="G14" t="s">
-        <v>151</v>
+        <v>198</v>
       </c>
       <c r="H14" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="I14" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="J14" t="s">
         <v>42</v>
@@ -2774,31 +3407,31 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="C15" t="s">
-        <v>155</v>
+        <v>202</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="E15" t="s">
-        <v>156</v>
+        <v>203</v>
       </c>
       <c r="F15" t="s">
-        <v>157</v>
+        <v>204</v>
       </c>
       <c r="G15" t="s">
-        <v>158</v>
+        <v>205</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="I15" t="s">
-        <v>159</v>
+        <v>206</v>
       </c>
       <c r="J15" t="s">
         <v>42</v>
@@ -2809,31 +3442,31 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="B16" t="s">
-        <v>161</v>
+        <v>208</v>
       </c>
       <c r="C16" t="s">
-        <v>162</v>
+        <v>209</v>
       </c>
       <c r="D16" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="E16" t="s">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="F16" t="s">
-        <v>165</v>
+        <v>212</v>
       </c>
       <c r="G16" t="s">
-        <v>166</v>
+        <v>213</v>
       </c>
       <c r="H16" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="I16" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="J16" t="s">
         <v>42</v>
@@ -2844,31 +3477,31 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s">
-        <v>169</v>
+        <v>216</v>
       </c>
       <c r="C17" t="s">
-        <v>170</v>
+        <v>217</v>
       </c>
       <c r="D17" t="s">
-        <v>171</v>
+        <v>218</v>
       </c>
       <c r="E17" t="s">
-        <v>172</v>
+        <v>219</v>
       </c>
       <c r="F17" t="s">
-        <v>173</v>
+        <v>220</v>
       </c>
       <c r="G17" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="H17" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I17" t="s">
-        <v>174</v>
+        <v>221</v>
       </c>
       <c r="J17" t="s">
         <v>42</v>
@@ -2879,31 +3512,31 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="C18" t="s">
-        <v>176</v>
+        <v>223</v>
       </c>
       <c r="D18" t="s">
-        <v>123</v>
+        <v>173</v>
       </c>
       <c r="E18" t="s">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="F18" t="s">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="G18" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="H18" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="I18" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="J18" t="s">
         <v>42</v>
@@ -2914,31 +3547,31 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="C19" t="s">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="D19" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="E19" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="F19" t="s">
-        <v>186</v>
+        <v>233</v>
       </c>
       <c r="G19" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="H19" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I19" t="s">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="J19" t="s">
         <v>42</v>
@@ -2949,31 +3582,31 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>236</v>
       </c>
       <c r="D20" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="E20" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="F20" t="s">
-        <v>191</v>
+        <v>238</v>
       </c>
       <c r="G20" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="H20" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I20" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="J20" t="s">
         <v>42</v>
@@ -2984,31 +3617,31 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="C21" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="E21" t="s">
-        <v>195</v>
+        <v>242</v>
       </c>
       <c r="F21" t="s">
-        <v>196</v>
+        <v>243</v>
       </c>
       <c r="G21" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="H21" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I21" t="s">
-        <v>198</v>
+        <v>245</v>
       </c>
       <c r="J21" t="s">
         <v>42</v>
@@ -3019,31 +3652,31 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="B22" t="s">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="C22" t="s">
-        <v>200</v>
+        <v>247</v>
       </c>
       <c r="D22" t="s">
-        <v>201</v>
+        <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>202</v>
+        <v>248</v>
       </c>
       <c r="F22" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="G22" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="H22" t="s">
-        <v>205</v>
+        <v>111</v>
       </c>
       <c r="I22" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="J22" t="s">
         <v>42</v>
@@ -3054,31 +3687,31 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>160</v>
+        <v>207</v>
       </c>
       <c r="B23" t="s">
-        <v>207</v>
+        <v>251</v>
       </c>
       <c r="C23" t="s">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="D23" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="E23" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="F23" t="s">
-        <v>211</v>
+        <v>255</v>
       </c>
       <c r="G23" t="s">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="H23" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="I23" t="s">
-        <v>213</v>
+        <v>257</v>
       </c>
       <c r="J23" t="s">
         <v>42</v>
@@ -3089,31 +3722,31 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>258</v>
+      </c>
+      <c r="B24" t="s">
+        <v>259</v>
+      </c>
+      <c r="C24" t="s">
+        <v>260</v>
+      </c>
+      <c r="D24" t="s">
+        <v>261</v>
+      </c>
+      <c r="E24" t="s">
+        <v>262</v>
+      </c>
+      <c r="F24" t="s">
+        <v>263</v>
+      </c>
+      <c r="G24" t="s">
+        <v>264</v>
+      </c>
+      <c r="H24" t="s">
         <v>214</v>
       </c>
-      <c r="B24" t="s">
-        <v>215</v>
-      </c>
-      <c r="C24" t="s">
-        <v>216</v>
-      </c>
-      <c r="D24" t="s">
-        <v>217</v>
-      </c>
-      <c r="E24" t="s">
-        <v>218</v>
-      </c>
-      <c r="F24" t="s">
-        <v>219</v>
-      </c>
-      <c r="G24" t="s">
-        <v>220</v>
-      </c>
-      <c r="H24" t="s">
-        <v>167</v>
-      </c>
       <c r="I24" t="s">
-        <v>221</v>
+        <v>265</v>
       </c>
       <c r="J24" t="s">
         <v>42</v>
@@ -3124,31 +3757,31 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s">
-        <v>222</v>
+        <v>266</v>
       </c>
       <c r="C25" t="s">
-        <v>223</v>
+        <v>267</v>
       </c>
       <c r="D25" t="s">
-        <v>224</v>
+        <v>268</v>
       </c>
       <c r="E25" t="s">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="F25" t="s">
-        <v>226</v>
+        <v>270</v>
       </c>
       <c r="G25" t="s">
-        <v>227</v>
+        <v>271</v>
       </c>
       <c r="H25" t="s">
-        <v>228</v>
+        <v>272</v>
       </c>
       <c r="I25" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="J25" t="s">
         <v>42</v>
@@ -3159,31 +3792,31 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="C26" t="s">
-        <v>230</v>
+        <v>274</v>
       </c>
       <c r="D26" t="s">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="E26" t="s">
-        <v>232</v>
+        <v>276</v>
       </c>
       <c r="F26" t="s">
-        <v>233</v>
+        <v>277</v>
       </c>
       <c r="G26" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="H26" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="I26" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="J26" t="s">
         <v>42</v>
@@ -3194,28 +3827,28 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s">
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>234</v>
+        <v>278</v>
       </c>
       <c r="D27" t="s">
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>235</v>
+        <v>279</v>
       </c>
       <c r="F27" t="s">
-        <v>236</v>
+        <v>280</v>
       </c>
       <c r="G27" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="H27" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="I27" t="s">
         <v>32</v>
@@ -3229,31 +3862,31 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="B28" t="s">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="C28" t="s">
-        <v>238</v>
+        <v>282</v>
       </c>
       <c r="D28" t="s">
-        <v>239</v>
+        <v>283</v>
       </c>
       <c r="E28" t="s">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="F28" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="G28" t="s">
-        <v>242</v>
+        <v>286</v>
       </c>
       <c r="H28" t="s">
-        <v>243</v>
+        <v>287</v>
       </c>
       <c r="I28" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="J28" t="s">
         <v>42</v>
@@ -3264,31 +3897,31 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s">
-        <v>245</v>
+        <v>289</v>
       </c>
       <c r="C29" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="D29" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="E29" t="s">
-        <v>248</v>
+        <v>292</v>
       </c>
       <c r="F29" t="s">
-        <v>249</v>
+        <v>293</v>
       </c>
       <c r="G29" t="s">
-        <v>250</v>
+        <v>294</v>
       </c>
       <c r="H29" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="I29" t="s">
-        <v>252</v>
+        <v>296</v>
       </c>
       <c r="J29" t="s">
         <v>42</v>
@@ -3299,31 +3932,31 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s">
-        <v>253</v>
+        <v>297</v>
       </c>
       <c r="C30" t="s">
-        <v>254</v>
+        <v>298</v>
       </c>
       <c r="D30" t="s">
-        <v>255</v>
+        <v>299</v>
       </c>
       <c r="E30" t="s">
-        <v>256</v>
+        <v>300</v>
       </c>
       <c r="F30" t="s">
-        <v>257</v>
+        <v>301</v>
       </c>
       <c r="G30" t="s">
-        <v>151</v>
+        <v>198</v>
       </c>
       <c r="H30" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="I30" t="s">
-        <v>258</v>
+        <v>302</v>
       </c>
       <c r="J30" t="s">
         <v>42</v>
@@ -3334,31 +3967,31 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="C31" t="s">
-        <v>261</v>
+        <v>305</v>
       </c>
       <c r="D31" t="s">
-        <v>262</v>
+        <v>306</v>
       </c>
       <c r="E31" t="s">
-        <v>263</v>
+        <v>307</v>
       </c>
       <c r="F31" t="s">
-        <v>264</v>
+        <v>308</v>
       </c>
       <c r="G31" t="s">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="H31" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I31" t="s">
-        <v>266</v>
+        <v>310</v>
       </c>
       <c r="J31" t="s">
         <v>42</v>
@@ -3369,31 +4002,31 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s">
-        <v>222</v>
+        <v>266</v>
       </c>
       <c r="C32" t="s">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="D32" t="s">
-        <v>224</v>
+        <v>268</v>
       </c>
       <c r="E32" t="s">
-        <v>268</v>
+        <v>312</v>
       </c>
       <c r="F32" t="s">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="G32" t="s">
-        <v>227</v>
+        <v>271</v>
       </c>
       <c r="H32" t="s">
-        <v>228</v>
+        <v>272</v>
       </c>
       <c r="I32" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="J32" t="s">
         <v>42</v>
@@ -3404,31 +4037,31 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="C33" t="s">
-        <v>230</v>
+        <v>274</v>
       </c>
       <c r="D33" t="s">
-        <v>270</v>
+        <v>314</v>
       </c>
       <c r="E33" t="s">
-        <v>271</v>
+        <v>315</v>
       </c>
       <c r="F33" t="s">
-        <v>272</v>
+        <v>316</v>
       </c>
       <c r="G33" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="H33" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="I33" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="J33" t="s">
         <v>42</v>
@@ -3439,31 +4072,31 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s">
-        <v>273</v>
+        <v>317</v>
       </c>
       <c r="C34" t="s">
-        <v>274</v>
+        <v>318</v>
       </c>
       <c r="D34" t="s">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="E34" t="s">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="F34" t="s">
-        <v>277</v>
+        <v>321</v>
       </c>
       <c r="G34" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="H34" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I34" t="s">
-        <v>278</v>
+        <v>322</v>
       </c>
       <c r="J34" t="s">
         <v>42</v>
@@ -3474,31 +4107,31 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
       <c r="C35" t="s">
-        <v>280</v>
+        <v>324</v>
       </c>
       <c r="D35" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="E35" t="s">
-        <v>281</v>
+        <v>325</v>
       </c>
       <c r="F35" t="s">
-        <v>282</v>
+        <v>326</v>
       </c>
       <c r="G35" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="H35" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I35" t="s">
-        <v>283</v>
+        <v>327</v>
       </c>
       <c r="J35" t="s">
         <v>42</v>
@@ -3509,31 +4142,31 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>284</v>
+        <v>328</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="C36" t="s">
-        <v>285</v>
+        <v>329</v>
       </c>
       <c r="D36" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="E36" t="s">
-        <v>287</v>
+        <v>331</v>
       </c>
       <c r="F36" t="s">
-        <v>288</v>
+        <v>332</v>
       </c>
       <c r="G36" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="H36" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="I36" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="J36" t="s">
         <v>42</v>
@@ -3544,31 +4177,31 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>284</v>
+        <v>328</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="C37" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="D37" t="s">
-        <v>290</v>
+        <v>334</v>
       </c>
       <c r="E37" t="s">
-        <v>291</v>
+        <v>335</v>
       </c>
       <c r="F37" t="s">
-        <v>292</v>
+        <v>336</v>
       </c>
       <c r="G37" t="s">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="H37" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="I37" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="J37" t="s">
         <v>42</v>
@@ -3579,31 +4212,31 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>284</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s">
-        <v>293</v>
+        <v>337</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>182</v>
       </c>
       <c r="D38" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="E38" t="s">
-        <v>294</v>
+        <v>338</v>
       </c>
       <c r="F38" t="s">
-        <v>295</v>
+        <v>339</v>
       </c>
       <c r="G38" t="s">
-        <v>296</v>
+        <v>340</v>
       </c>
       <c r="H38" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I38" t="s">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="J38" t="s">
         <v>42</v>
@@ -3614,31 +4247,31 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>284</v>
+        <v>328</v>
       </c>
       <c r="B39" t="s">
-        <v>279</v>
+        <v>323</v>
       </c>
       <c r="C39" t="s">
-        <v>280</v>
+        <v>324</v>
       </c>
       <c r="D39" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="E39" t="s">
-        <v>298</v>
+        <v>342</v>
       </c>
       <c r="F39" t="s">
-        <v>299</v>
+        <v>343</v>
       </c>
       <c r="G39" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="H39" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I39" t="s">
-        <v>283</v>
+        <v>327</v>
       </c>
       <c r="J39" t="s">
         <v>42</v>
@@ -3649,31 +4282,31 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>300</v>
+        <v>344</v>
       </c>
       <c r="B40" t="s">
-        <v>301</v>
+        <v>345</v>
       </c>
       <c r="C40" t="s">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>347</v>
       </c>
       <c r="E40" t="s">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="F40" t="s">
-        <v>305</v>
+        <v>349</v>
       </c>
       <c r="G40" t="s">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="H40" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="I40" t="s">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="J40" t="s">
         <v>42</v>
@@ -3684,31 +4317,31 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>300</v>
+        <v>344</v>
       </c>
       <c r="B41" t="s">
-        <v>308</v>
+        <v>352</v>
       </c>
       <c r="C41" t="s">
-        <v>162</v>
+        <v>209</v>
       </c>
       <c r="D41" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="E41" t="s">
-        <v>309</v>
+        <v>353</v>
       </c>
       <c r="F41" t="s">
-        <v>310</v>
+        <v>354</v>
       </c>
       <c r="G41" t="s">
-        <v>311</v>
+        <v>355</v>
       </c>
       <c r="H41" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="I41" t="s">
-        <v>312</v>
+        <v>356</v>
       </c>
       <c r="J41" t="s">
         <v>42</v>
@@ -3719,31 +4352,31 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>300</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s">
-        <v>313</v>
+        <v>357</v>
       </c>
       <c r="C42" t="s">
-        <v>314</v>
+        <v>358</v>
       </c>
       <c r="D42" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="E42" t="s">
-        <v>315</v>
+        <v>359</v>
       </c>
       <c r="F42" t="s">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="G42" t="s">
-        <v>311</v>
+        <v>355</v>
       </c>
       <c r="H42" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="I42" t="s">
-        <v>317</v>
+        <v>361</v>
       </c>
       <c r="J42" t="s">
         <v>42</v>
@@ -3754,31 +4387,31 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>300</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s">
-        <v>318</v>
+        <v>362</v>
       </c>
       <c r="C43" t="s">
-        <v>319</v>
+        <v>363</v>
       </c>
       <c r="D43" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="E43" t="s">
-        <v>320</v>
+        <v>364</v>
       </c>
       <c r="F43" t="s">
-        <v>321</v>
+        <v>365</v>
       </c>
       <c r="G43" t="s">
-        <v>322</v>
+        <v>366</v>
       </c>
       <c r="H43" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="I43" t="s">
-        <v>323</v>
+        <v>367</v>
       </c>
       <c r="J43" t="s">
         <v>42</v>
@@ -3789,31 +4422,31 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>300</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s">
-        <v>324</v>
+        <v>368</v>
       </c>
       <c r="C44" t="s">
-        <v>325</v>
+        <v>369</v>
       </c>
       <c r="D44" t="s">
-        <v>201</v>
+        <v>67</v>
       </c>
       <c r="E44" t="s">
-        <v>326</v>
+        <v>370</v>
       </c>
       <c r="F44" t="s">
-        <v>327</v>
+        <v>371</v>
       </c>
       <c r="G44" t="s">
-        <v>328</v>
+        <v>372</v>
       </c>
       <c r="H44" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="I44" t="s">
-        <v>329</v>
+        <v>373</v>
       </c>
       <c r="J44" t="s">
         <v>42</v>
@@ -3824,31 +4457,31 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>300</v>
+        <v>344</v>
       </c>
       <c r="B45" t="s">
-        <v>330</v>
+        <v>374</v>
       </c>
       <c r="C45" t="s">
-        <v>331</v>
+        <v>375</v>
       </c>
       <c r="D45" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="E45" t="s">
-        <v>332</v>
+        <v>376</v>
       </c>
       <c r="F45" t="s">
-        <v>333</v>
+        <v>377</v>
       </c>
       <c r="G45" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="H45" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I45" t="s">
-        <v>334</v>
+        <v>378</v>
       </c>
       <c r="J45" t="s">
         <v>42</v>
@@ -3859,31 +4492,31 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>300</v>
+        <v>344</v>
       </c>
       <c r="B46" t="s">
-        <v>335</v>
+        <v>379</v>
       </c>
       <c r="C46" t="s">
-        <v>336</v>
+        <v>380</v>
       </c>
       <c r="D46" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="E46" t="s">
-        <v>337</v>
+        <v>381</v>
       </c>
       <c r="F46" t="s">
-        <v>338</v>
+        <v>382</v>
       </c>
       <c r="G46" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="H46" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="I46" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="J46" t="s">
         <v>42</v>
@@ -3894,31 +4527,31 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B47" t="s">
-        <v>301</v>
+        <v>345</v>
       </c>
       <c r="C47" t="s">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="D47" t="s">
-        <v>303</v>
+        <v>347</v>
       </c>
       <c r="E47" t="s">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="F47" t="s">
-        <v>305</v>
+        <v>349</v>
       </c>
       <c r="G47" t="s">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="H47" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="I47" t="s">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="J47" t="s">
         <v>42</v>
@@ -3929,31 +4562,31 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B48" t="s">
-        <v>308</v>
+        <v>352</v>
       </c>
       <c r="C48" t="s">
-        <v>162</v>
+        <v>209</v>
       </c>
       <c r="D48" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="E48" t="s">
-        <v>309</v>
+        <v>353</v>
       </c>
       <c r="F48" t="s">
-        <v>310</v>
+        <v>354</v>
       </c>
       <c r="G48" t="s">
-        <v>311</v>
+        <v>355</v>
       </c>
       <c r="H48" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="I48" t="s">
-        <v>312</v>
+        <v>356</v>
       </c>
       <c r="J48" t="s">
         <v>42</v>
@@ -3964,31 +4597,31 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B49" t="s">
-        <v>313</v>
+        <v>357</v>
       </c>
       <c r="C49" t="s">
-        <v>314</v>
+        <v>358</v>
       </c>
       <c r="D49" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="E49" t="s">
-        <v>315</v>
+        <v>359</v>
       </c>
       <c r="F49" t="s">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="G49" t="s">
-        <v>311</v>
+        <v>355</v>
       </c>
       <c r="H49" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="I49" t="s">
-        <v>317</v>
+        <v>361</v>
       </c>
       <c r="J49" t="s">
         <v>42</v>
@@ -3999,31 +4632,31 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B50" t="s">
-        <v>318</v>
+        <v>362</v>
       </c>
       <c r="C50" t="s">
-        <v>319</v>
+        <v>363</v>
       </c>
       <c r="D50" t="s">
-        <v>286</v>
+        <v>330</v>
       </c>
       <c r="E50" t="s">
-        <v>320</v>
+        <v>364</v>
       </c>
       <c r="F50" t="s">
-        <v>321</v>
+        <v>365</v>
       </c>
       <c r="G50" t="s">
-        <v>322</v>
+        <v>366</v>
       </c>
       <c r="H50" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="I50" t="s">
-        <v>323</v>
+        <v>367</v>
       </c>
       <c r="J50" t="s">
         <v>42</v>
@@ -4034,31 +4667,31 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s">
-        <v>324</v>
+        <v>368</v>
       </c>
       <c r="C51" t="s">
-        <v>325</v>
+        <v>369</v>
       </c>
       <c r="D51" t="s">
-        <v>201</v>
+        <v>67</v>
       </c>
       <c r="E51" t="s">
-        <v>326</v>
+        <v>370</v>
       </c>
       <c r="F51" t="s">
-        <v>327</v>
+        <v>371</v>
       </c>
       <c r="G51" t="s">
-        <v>328</v>
+        <v>372</v>
       </c>
       <c r="H51" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="I51" t="s">
-        <v>329</v>
+        <v>373</v>
       </c>
       <c r="J51" t="s">
         <v>42</v>
@@ -4069,31 +4702,31 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B52" t="s">
-        <v>330</v>
+        <v>374</v>
       </c>
       <c r="C52" t="s">
-        <v>331</v>
+        <v>375</v>
       </c>
       <c r="D52" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="E52" t="s">
-        <v>332</v>
+        <v>376</v>
       </c>
       <c r="F52" t="s">
-        <v>333</v>
+        <v>377</v>
       </c>
       <c r="G52" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="H52" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I52" t="s">
-        <v>334</v>
+        <v>378</v>
       </c>
       <c r="J52" t="s">
         <v>42</v>
@@ -4104,31 +4737,31 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B53" t="s">
-        <v>335</v>
+        <v>379</v>
       </c>
       <c r="C53" t="s">
-        <v>336</v>
+        <v>380</v>
       </c>
       <c r="D53" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="E53" t="s">
-        <v>337</v>
+        <v>381</v>
       </c>
       <c r="F53" t="s">
-        <v>338</v>
+        <v>382</v>
       </c>
       <c r="G53" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="H53" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="I53" t="s">
-        <v>339</v>
+        <v>383</v>
       </c>
       <c r="J53" t="s">
         <v>42</v>
@@ -4139,31 +4772,31 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B54" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="C54" t="s">
-        <v>342</v>
+        <v>386</v>
       </c>
       <c r="D54" t="s">
-        <v>343</v>
+        <v>387</v>
       </c>
       <c r="E54" t="s">
-        <v>344</v>
+        <v>388</v>
       </c>
       <c r="F54" t="s">
-        <v>345</v>
+        <v>389</v>
       </c>
       <c r="G54" t="s">
-        <v>346</v>
+        <v>390</v>
       </c>
       <c r="H54" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I54" t="s">
-        <v>347</v>
+        <v>391</v>
       </c>
       <c r="J54" t="s">
         <v>42</v>
@@ -4174,31 +4807,31 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B55" t="s">
-        <v>348</v>
+        <v>392</v>
       </c>
       <c r="C55" t="s">
-        <v>349</v>
+        <v>393</v>
       </c>
       <c r="D55" t="s">
-        <v>350</v>
+        <v>394</v>
       </c>
       <c r="E55" t="s">
-        <v>351</v>
+        <v>395</v>
       </c>
       <c r="F55" t="s">
-        <v>352</v>
+        <v>396</v>
       </c>
       <c r="G55" t="s">
-        <v>353</v>
+        <v>397</v>
       </c>
       <c r="H55" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="I55" t="s">
-        <v>354</v>
+        <v>398</v>
       </c>
       <c r="J55" t="s">
         <v>42</v>
@@ -4209,31 +4842,31 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B56" t="s">
-        <v>355</v>
+        <v>399</v>
       </c>
       <c r="C56" t="s">
-        <v>356</v>
+        <v>400</v>
       </c>
       <c r="D56" t="s">
-        <v>357</v>
+        <v>401</v>
       </c>
       <c r="E56" t="s">
-        <v>358</v>
+        <v>402</v>
       </c>
       <c r="F56" t="s">
-        <v>359</v>
+        <v>403</v>
       </c>
       <c r="G56" t="s">
-        <v>360</v>
+        <v>404</v>
       </c>
       <c r="H56" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="I56" t="s">
-        <v>361</v>
+        <v>405</v>
       </c>
       <c r="J56" t="s">
         <v>42</v>
@@ -4244,31 +4877,31 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B57" t="s">
-        <v>362</v>
+        <v>406</v>
       </c>
       <c r="C57" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="D57" t="s">
-        <v>357</v>
+        <v>401</v>
       </c>
       <c r="E57" t="s">
-        <v>364</v>
+        <v>408</v>
       </c>
       <c r="F57" t="s">
-        <v>365</v>
+        <v>409</v>
       </c>
       <c r="G57" t="s">
-        <v>366</v>
+        <v>410</v>
       </c>
       <c r="H57" t="s">
-        <v>243</v>
+        <v>287</v>
       </c>
       <c r="I57" t="s">
-        <v>367</v>
+        <v>411</v>
       </c>
       <c r="J57" t="s">
         <v>42</v>
@@ -4279,31 +4912,31 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B58" t="s">
-        <v>368</v>
+        <v>412</v>
       </c>
       <c r="C58" t="s">
-        <v>369</v>
+        <v>413</v>
       </c>
       <c r="D58" t="s">
-        <v>357</v>
+        <v>401</v>
       </c>
       <c r="E58" t="s">
-        <v>370</v>
+        <v>414</v>
       </c>
       <c r="F58" t="s">
-        <v>371</v>
+        <v>415</v>
       </c>
       <c r="G58" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="H58" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="I58" t="s">
-        <v>372</v>
+        <v>416</v>
       </c>
       <c r="J58" t="s">
         <v>42</v>
@@ -4314,31 +4947,31 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B59" t="s">
-        <v>373</v>
+        <v>417</v>
       </c>
       <c r="C59" t="s">
-        <v>374</v>
+        <v>418</v>
       </c>
       <c r="D59" t="s">
-        <v>375</v>
+        <v>419</v>
       </c>
       <c r="E59" t="s">
-        <v>376</v>
+        <v>420</v>
       </c>
       <c r="F59" t="s">
-        <v>377</v>
+        <v>421</v>
       </c>
       <c r="G59" t="s">
-        <v>360</v>
+        <v>404</v>
       </c>
       <c r="H59" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="I59" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
       <c r="J59" t="s">
         <v>42</v>
@@ -4349,31 +4982,31 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B60" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
       <c r="C60" t="s">
-        <v>380</v>
+        <v>424</v>
       </c>
       <c r="D60" t="s">
-        <v>381</v>
+        <v>425</v>
       </c>
       <c r="E60" t="s">
-        <v>382</v>
+        <v>426</v>
       </c>
       <c r="F60" t="s">
-        <v>383</v>
+        <v>427</v>
       </c>
       <c r="G60" t="s">
-        <v>384</v>
+        <v>428</v>
       </c>
       <c r="H60" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I60" t="s">
-        <v>385</v>
+        <v>429</v>
       </c>
       <c r="J60" t="s">
         <v>42</v>
@@ -4384,31 +5017,31 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B61" t="s">
-        <v>386</v>
+        <v>430</v>
       </c>
       <c r="C61" t="s">
-        <v>387</v>
+        <v>431</v>
       </c>
       <c r="D61" t="s">
-        <v>388</v>
+        <v>432</v>
       </c>
       <c r="E61" t="s">
-        <v>389</v>
+        <v>433</v>
       </c>
       <c r="F61" t="s">
-        <v>390</v>
+        <v>434</v>
       </c>
       <c r="G61" t="s">
-        <v>391</v>
+        <v>435</v>
       </c>
       <c r="H61" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="I61" t="s">
-        <v>392</v>
+        <v>436</v>
       </c>
       <c r="J61" t="s">
         <v>42</v>
@@ -4419,31 +5052,31 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B62" t="s">
-        <v>393</v>
+        <v>437</v>
       </c>
       <c r="C62" t="s">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="D62" t="s">
-        <v>388</v>
+        <v>432</v>
       </c>
       <c r="E62" t="s">
-        <v>395</v>
+        <v>439</v>
       </c>
       <c r="F62" t="s">
-        <v>396</v>
+        <v>440</v>
       </c>
       <c r="G62" t="s">
-        <v>391</v>
+        <v>435</v>
       </c>
       <c r="H62" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="I62" t="s">
-        <v>397</v>
+        <v>441</v>
       </c>
       <c r="J62" t="s">
         <v>42</v>
@@ -4454,31 +5087,31 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B63" t="s">
-        <v>398</v>
+        <v>442</v>
       </c>
       <c r="C63" t="s">
-        <v>399</v>
+        <v>443</v>
       </c>
       <c r="D63" t="s">
-        <v>400</v>
+        <v>444</v>
       </c>
       <c r="E63" t="s">
-        <v>401</v>
+        <v>445</v>
       </c>
       <c r="F63" t="s">
-        <v>402</v>
+        <v>446</v>
       </c>
       <c r="G63" t="s">
-        <v>328</v>
+        <v>372</v>
       </c>
       <c r="H63" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="I63" t="s">
-        <v>403</v>
+        <v>447</v>
       </c>
       <c r="J63" t="s">
         <v>42</v>
@@ -4489,31 +5122,31 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B64" t="s">
-        <v>404</v>
+        <v>448</v>
       </c>
       <c r="C64" t="s">
-        <v>405</v>
+        <v>449</v>
       </c>
       <c r="D64" t="s">
-        <v>406</v>
+        <v>450</v>
       </c>
       <c r="E64" t="s">
-        <v>407</v>
+        <v>451</v>
       </c>
       <c r="F64" t="s">
-        <v>408</v>
+        <v>452</v>
       </c>
       <c r="G64" t="s">
-        <v>409</v>
+        <v>453</v>
       </c>
       <c r="H64" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="I64" t="s">
-        <v>410</v>
+        <v>454</v>
       </c>
       <c r="J64" t="s">
         <v>42</v>
@@ -4524,31 +5157,31 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B65" t="s">
-        <v>411</v>
+        <v>455</v>
       </c>
       <c r="C65" t="s">
-        <v>412</v>
+        <v>456</v>
       </c>
       <c r="D65" t="s">
-        <v>413</v>
+        <v>457</v>
       </c>
       <c r="E65" t="s">
-        <v>414</v>
+        <v>458</v>
       </c>
       <c r="F65" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="G65" t="s">
-        <v>416</v>
+        <v>460</v>
       </c>
       <c r="H65" t="s">
-        <v>417</v>
+        <v>461</v>
       </c>
       <c r="I65" t="s">
-        <v>418</v>
+        <v>462</v>
       </c>
       <c r="J65" t="s">
         <v>42</v>
@@ -4559,31 +5192,31 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B66" t="s">
-        <v>419</v>
+        <v>463</v>
       </c>
       <c r="C66" t="s">
-        <v>420</v>
+        <v>464</v>
       </c>
       <c r="D66" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="E66" t="s">
-        <v>421</v>
+        <v>465</v>
       </c>
       <c r="F66" t="s">
         <v>35</v>
       </c>
       <c r="G66" t="s">
-        <v>422</v>
+        <v>466</v>
       </c>
       <c r="H66" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="I66" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="J66" t="s">
         <v>42</v>
@@ -4594,31 +5227,31 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>424</v>
+        <v>468</v>
       </c>
       <c r="B67" t="s">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="C67" t="s">
-        <v>426</v>
+        <v>470</v>
       </c>
       <c r="D67" t="s">
-        <v>303</v>
+        <v>347</v>
       </c>
       <c r="E67" t="s">
-        <v>427</v>
+        <v>471</v>
       </c>
       <c r="F67" t="s">
-        <v>428</v>
+        <v>472</v>
       </c>
       <c r="G67" t="s">
-        <v>429</v>
+        <v>473</v>
       </c>
       <c r="H67" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="I67" t="s">
-        <v>430</v>
+        <v>474</v>
       </c>
       <c r="J67" t="s">
         <v>42</v>
@@ -4629,31 +5262,31 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>424</v>
+        <v>468</v>
       </c>
       <c r="B68" t="s">
-        <v>431</v>
+        <v>475</v>
       </c>
       <c r="C68" t="s">
-        <v>432</v>
+        <v>476</v>
       </c>
       <c r="D68" t="s">
-        <v>433</v>
+        <v>477</v>
       </c>
       <c r="E68" t="s">
-        <v>434</v>
+        <v>478</v>
       </c>
       <c r="F68" t="s">
-        <v>435</v>
+        <v>479</v>
       </c>
       <c r="G68" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="H68" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I68" t="s">
-        <v>436</v>
+        <v>480</v>
       </c>
       <c r="J68" t="s">
         <v>42</v>
@@ -4664,31 +5297,31 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>424</v>
+        <v>468</v>
       </c>
       <c r="B69" t="s">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="C69" t="s">
-        <v>438</v>
+        <v>481</v>
       </c>
       <c r="D69" t="s">
-        <v>439</v>
+        <v>79</v>
       </c>
       <c r="E69" t="s">
-        <v>440</v>
+        <v>482</v>
       </c>
       <c r="F69" t="s">
-        <v>441</v>
+        <v>483</v>
       </c>
       <c r="G69" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="H69" t="s">
-        <v>205</v>
+        <v>111</v>
       </c>
       <c r="I69" t="s">
-        <v>442</v>
+        <v>76</v>
       </c>
       <c r="J69" t="s">
         <v>42</v>
@@ -4699,31 +5332,31 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>424</v>
+        <v>468</v>
       </c>
       <c r="B70" t="s">
-        <v>443</v>
+        <v>484</v>
       </c>
       <c r="C70" t="s">
-        <v>444</v>
+        <v>485</v>
       </c>
       <c r="D70" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="E70" t="s">
-        <v>445</v>
+        <v>486</v>
       </c>
       <c r="F70" t="s">
-        <v>446</v>
+        <v>487</v>
       </c>
       <c r="G70" t="s">
-        <v>296</v>
+        <v>340</v>
       </c>
       <c r="H70" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I70" t="s">
-        <v>447</v>
+        <v>488</v>
       </c>
       <c r="J70" t="s">
         <v>42</v>
@@ -4734,31 +5367,31 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>448</v>
+        <v>489</v>
       </c>
       <c r="B71" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="C71" t="s">
-        <v>449</v>
+        <v>490</v>
       </c>
       <c r="D71" t="s">
-        <v>450</v>
+        <v>491</v>
       </c>
       <c r="E71" t="s">
-        <v>451</v>
+        <v>492</v>
       </c>
       <c r="F71" t="s">
-        <v>452</v>
+        <v>493</v>
       </c>
       <c r="G71" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="H71" t="s">
-        <v>453</v>
+        <v>494</v>
       </c>
       <c r="I71" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="J71" t="s">
         <v>42</v>
@@ -4769,31 +5402,31 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>448</v>
+        <v>489</v>
       </c>
       <c r="B72" t="s">
-        <v>454</v>
+        <v>495</v>
       </c>
       <c r="C72" t="s">
-        <v>455</v>
+        <v>496</v>
       </c>
       <c r="D72" t="s">
-        <v>456</v>
+        <v>497</v>
       </c>
       <c r="E72" t="s">
-        <v>457</v>
+        <v>498</v>
       </c>
       <c r="F72" t="s">
-        <v>458</v>
+        <v>499</v>
       </c>
       <c r="G72" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="H72" t="s">
-        <v>453</v>
+        <v>494</v>
       </c>
       <c r="I72" t="s">
-        <v>459</v>
+        <v>500</v>
       </c>
       <c r="J72" t="s">
         <v>42</v>
@@ -4804,31 +5437,31 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>448</v>
+        <v>489</v>
       </c>
       <c r="B73" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="C73" t="s">
-        <v>461</v>
+        <v>502</v>
       </c>
       <c r="D73" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="E73" t="s">
-        <v>462</v>
+        <v>503</v>
       </c>
       <c r="F73" t="s">
-        <v>463</v>
+        <v>504</v>
       </c>
       <c r="G73" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="H73" t="s">
-        <v>453</v>
+        <v>494</v>
       </c>
       <c r="I73" t="s">
-        <v>464</v>
+        <v>505</v>
       </c>
       <c r="J73" t="s">
         <v>42</v>
@@ -4839,31 +5472,31 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>448</v>
+        <v>489</v>
       </c>
       <c r="B74" t="s">
-        <v>465</v>
+        <v>506</v>
       </c>
       <c r="C74" t="s">
-        <v>466</v>
+        <v>507</v>
       </c>
       <c r="D74" t="s">
-        <v>209</v>
+        <v>253</v>
       </c>
       <c r="E74" t="s">
-        <v>467</v>
+        <v>508</v>
       </c>
       <c r="F74" t="s">
-        <v>468</v>
+        <v>509</v>
       </c>
       <c r="G74" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="H74" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I74" t="s">
-        <v>469</v>
+        <v>510</v>
       </c>
       <c r="J74" t="s">
         <v>42</v>
@@ -4874,31 +5507,31 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>448</v>
+        <v>489</v>
       </c>
       <c r="B75" t="s">
-        <v>470</v>
+        <v>511</v>
       </c>
       <c r="C75" t="s">
-        <v>471</v>
+        <v>512</v>
       </c>
       <c r="D75" t="s">
-        <v>472</v>
+        <v>513</v>
       </c>
       <c r="E75" t="s">
-        <v>473</v>
+        <v>514</v>
       </c>
       <c r="F75" t="s">
-        <v>474</v>
+        <v>515</v>
       </c>
       <c r="G75" t="s">
-        <v>475</v>
+        <v>516</v>
       </c>
       <c r="H75" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I75" t="s">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="J75" t="s">
         <v>42</v>
@@ -4909,31 +5542,31 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>448</v>
+        <v>489</v>
       </c>
       <c r="B76" t="s">
-        <v>477</v>
+        <v>518</v>
       </c>
       <c r="C76" t="s">
-        <v>478</v>
+        <v>519</v>
       </c>
       <c r="D76" t="s">
-        <v>479</v>
+        <v>520</v>
       </c>
       <c r="E76" t="s">
-        <v>480</v>
+        <v>521</v>
       </c>
       <c r="F76" t="s">
-        <v>481</v>
+        <v>522</v>
       </c>
       <c r="G76" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="H76" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="I76" t="s">
-        <v>482</v>
+        <v>523</v>
       </c>
       <c r="J76" t="s">
         <v>42</v>
@@ -4944,31 +5577,31 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>448</v>
+        <v>489</v>
       </c>
       <c r="B77" t="s">
-        <v>483</v>
+        <v>524</v>
       </c>
       <c r="C77" t="s">
-        <v>484</v>
+        <v>525</v>
       </c>
       <c r="D77" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="E77" t="s">
-        <v>485</v>
+        <v>526</v>
       </c>
       <c r="F77" t="s">
-        <v>486</v>
+        <v>527</v>
       </c>
       <c r="G77" t="s">
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="H77" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="I77" t="s">
-        <v>488</v>
+        <v>529</v>
       </c>
       <c r="J77" t="s">
         <v>42</v>
@@ -4979,31 +5612,31 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="B78" t="s">
-        <v>490</v>
+        <v>531</v>
       </c>
       <c r="C78" t="s">
-        <v>491</v>
+        <v>532</v>
       </c>
       <c r="D78" t="s">
-        <v>492</v>
+        <v>533</v>
       </c>
       <c r="E78" t="s">
-        <v>493</v>
+        <v>534</v>
       </c>
       <c r="F78" t="s">
-        <v>494</v>
+        <v>535</v>
       </c>
       <c r="G78" t="s">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="H78" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="I78" t="s">
-        <v>496</v>
+        <v>537</v>
       </c>
       <c r="J78" t="s">
         <v>42</v>
@@ -5014,31 +5647,31 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="B79" t="s">
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="C79" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="D79" t="s">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="E79" t="s">
-        <v>498</v>
+        <v>539</v>
       </c>
       <c r="F79" t="s">
-        <v>499</v>
+        <v>540</v>
       </c>
       <c r="G79" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="H79" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="I79" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="J79" t="s">
         <v>42</v>
@@ -5049,31 +5682,31 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="B80" t="s">
-        <v>500</v>
+        <v>541</v>
       </c>
       <c r="C80" t="s">
-        <v>501</v>
+        <v>542</v>
       </c>
       <c r="D80" t="s">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="E80" t="s">
-        <v>502</v>
+        <v>543</v>
       </c>
       <c r="F80" t="s">
-        <v>503</v>
+        <v>544</v>
       </c>
       <c r="G80" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="H80" t="s">
-        <v>167</v>
+        <v>214</v>
       </c>
       <c r="I80" t="s">
-        <v>504</v>
+        <v>545</v>
       </c>
       <c r="J80" t="s">
         <v>42</v>
@@ -5084,31 +5717,31 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="B81" t="s">
-        <v>505</v>
+        <v>546</v>
       </c>
       <c r="C81" t="s">
-        <v>506</v>
+        <v>547</v>
       </c>
       <c r="D81" t="s">
-        <v>507</v>
+        <v>548</v>
       </c>
       <c r="E81" t="s">
-        <v>508</v>
+        <v>549</v>
       </c>
       <c r="F81" t="s">
-        <v>509</v>
+        <v>550</v>
       </c>
       <c r="G81" t="s">
-        <v>510</v>
+        <v>551</v>
       </c>
       <c r="H81" t="s">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="I81" t="s">
-        <v>512</v>
+        <v>553</v>
       </c>
       <c r="J81" t="s">
         <v>42</v>
@@ -5119,31 +5752,31 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="B82" t="s">
-        <v>470</v>
+        <v>511</v>
       </c>
       <c r="C82" t="s">
-        <v>471</v>
+        <v>512</v>
       </c>
       <c r="D82" t="s">
-        <v>513</v>
+        <v>554</v>
       </c>
       <c r="E82" t="s">
-        <v>514</v>
+        <v>555</v>
       </c>
       <c r="F82" t="s">
-        <v>515</v>
+        <v>556</v>
       </c>
       <c r="G82" t="s">
-        <v>475</v>
+        <v>516</v>
       </c>
       <c r="H82" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="I82" t="s">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="J82" t="s">
         <v>42</v>
@@ -5154,31 +5787,31 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="B83" t="s">
-        <v>516</v>
+        <v>557</v>
       </c>
       <c r="C83" t="s">
-        <v>517</v>
+        <v>558</v>
       </c>
       <c r="D83" t="s">
-        <v>479</v>
+        <v>520</v>
       </c>
       <c r="E83" t="s">
-        <v>518</v>
+        <v>559</v>
       </c>
       <c r="F83" t="s">
-        <v>519</v>
+        <v>560</v>
       </c>
       <c r="G83" t="s">
-        <v>520</v>
+        <v>561</v>
       </c>
       <c r="H83" t="s">
-        <v>521</v>
+        <v>562</v>
       </c>
       <c r="I83" t="s">
-        <v>522</v>
+        <v>563</v>
       </c>
       <c r="J83" t="s">
         <v>42</v>
@@ -5189,7 +5822,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="B84" t="s">
         <v>31</v>
@@ -5204,13 +5837,13 @@
         <v>38</v>
       </c>
       <c r="F84" t="s">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="G84" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="H84" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="I84" t="s">
         <v>32</v>
@@ -5219,6 +5852,146 @@
         <v>42</v>
       </c>
       <c r="K84" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>102</v>
+      </c>
+      <c r="B85" t="s">
+        <v>50</v>
+      </c>
+      <c r="C85" t="s">
+        <v>52</v>
+      </c>
+      <c r="D85" t="s">
+        <v>53</v>
+      </c>
+      <c r="E85" t="s">
+        <v>54</v>
+      </c>
+      <c r="F85" t="s">
+        <v>106</v>
+      </c>
+      <c r="G85" t="s">
+        <v>107</v>
+      </c>
+      <c r="H85" t="s">
+        <v>108</v>
+      </c>
+      <c r="I85" t="s">
+        <v>51</v>
+      </c>
+      <c r="J85" t="s">
+        <v>42</v>
+      </c>
+      <c r="K85" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>102</v>
+      </c>
+      <c r="B86" t="s">
+        <v>64</v>
+      </c>
+      <c r="C86" t="s">
+        <v>66</v>
+      </c>
+      <c r="D86" t="s">
+        <v>67</v>
+      </c>
+      <c r="E86" t="s">
+        <v>68</v>
+      </c>
+      <c r="F86" t="s">
+        <v>69</v>
+      </c>
+      <c r="G86" t="s">
+        <v>109</v>
+      </c>
+      <c r="H86" t="s">
+        <v>108</v>
+      </c>
+      <c r="I86" t="s">
+        <v>65</v>
+      </c>
+      <c r="J86" t="s">
+        <v>42</v>
+      </c>
+      <c r="K86" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>102</v>
+      </c>
+      <c r="B87" t="s">
+        <v>75</v>
+      </c>
+      <c r="C87" t="s">
+        <v>77</v>
+      </c>
+      <c r="D87" t="s">
+        <v>78</v>
+      </c>
+      <c r="E87" t="s">
+        <v>81</v>
+      </c>
+      <c r="F87" t="s">
+        <v>82</v>
+      </c>
+      <c r="G87" t="s">
+        <v>110</v>
+      </c>
+      <c r="H87" t="s">
+        <v>111</v>
+      </c>
+      <c r="I87" t="s">
+        <v>76</v>
+      </c>
+      <c r="J87" t="s">
+        <v>42</v>
+      </c>
+      <c r="K87" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>102</v>
+      </c>
+      <c r="B88" t="s">
+        <v>90</v>
+      </c>
+      <c r="C88" t="s">
+        <v>92</v>
+      </c>
+      <c r="D88" t="s">
+        <v>78</v>
+      </c>
+      <c r="E88" t="s">
+        <v>93</v>
+      </c>
+      <c r="F88" t="s">
+        <v>94</v>
+      </c>
+      <c r="G88" t="s">
+        <v>112</v>
+      </c>
+      <c r="H88" t="s">
+        <v>113</v>
+      </c>
+      <c r="I88" t="s">
+        <v>91</v>
+      </c>
+      <c r="J88" t="s">
+        <v>42</v>
+      </c>
+      <c r="K88" t="s">
         <v>30</v>
       </c>
     </row>
